--- a/map.xlsx
+++ b/map.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/phamxuanbac/Downloads/gamedev/Game03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7772C7D1-E0CE-CD49-891C-A390391C25A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14943FAB-797E-BA4C-B007-9EC7DA190F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440"/>
+    <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="map" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -868,7 +868,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CV41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -4823,7 +4823,7 @@
         <v>2</v>
       </c>
       <c r="BX15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BY15">
         <v>0</v>
@@ -5086,13 +5086,13 @@
         <v>800</v>
       </c>
       <c r="BV16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX16">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY16">
         <v>0</v>
@@ -5358,13 +5358,13 @@
         <v>800</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY17">
         <v>0</v>
@@ -5636,13 +5636,13 @@
         <v>800</v>
       </c>
       <c r="BV18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX18">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY18">
         <v>0</v>
@@ -5908,13 +5908,13 @@
         <v>128</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY19">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>128</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY20">
         <v>0</v>
@@ -6452,13 +6452,13 @@
         <v>128</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY21">
         <v>0</v>
@@ -6724,13 +6724,13 @@
         <v>128</v>
       </c>
       <c r="BV22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX22">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY22">
         <v>0</v>
@@ -6972,13 +6972,13 @@
         <v>800</v>
       </c>
       <c r="BV23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX23">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY23">
         <v>0</v>
@@ -7220,13 +7220,13 @@
         <v>800</v>
       </c>
       <c r="BV24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX24">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY24">
         <v>0</v>
@@ -7468,13 +7468,13 @@
         <v>800</v>
       </c>
       <c r="BV25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX25">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY25">
         <v>0</v>
@@ -7716,13 +7716,13 @@
         <v>800</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY26">
         <v>0</v>
@@ -7910,22 +7910,22 @@
         <v>356</v>
       </c>
       <c r="AL27">
-        <v>797</v>
+        <v>398.79700000000003</v>
       </c>
       <c r="AM27">
-        <v>798</v>
+        <v>399.798</v>
       </c>
       <c r="AN27">
-        <v>806</v>
+        <v>398.80599999999998</v>
       </c>
       <c r="AO27">
-        <v>794</v>
+        <v>419.79399999999998</v>
       </c>
       <c r="AP27">
-        <v>793</v>
+        <v>358.79300000000001</v>
       </c>
       <c r="AQ27">
-        <v>807</v>
+        <v>419.80700000000002</v>
       </c>
       <c r="AR27">
         <v>804</v>
@@ -7982,13 +7982,13 @@
         <v>800</v>
       </c>
       <c r="BV27">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW27">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX27">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY27">
         <v>0</v>
@@ -8176,25 +8176,25 @@
         <v>357</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>419</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>398</v>
       </c>
       <c r="AR28">
-        <v>803</v>
+        <v>357.803</v>
       </c>
       <c r="AS28">
         <v>799</v>
@@ -8248,13 +8248,13 @@
         <v>800</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>128</v>
       </c>
       <c r="BY28">
         <v>0</v>
@@ -8442,22 +8442,25 @@
         <v>358</v>
       </c>
       <c r="AL29">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="AM29">
-        <v>0</v>
+        <v>418</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>357</v>
       </c>
       <c r="AO29">
-        <v>144</v>
+        <v>358.14400000000001</v>
       </c>
       <c r="AP29">
-        <v>145</v>
+        <v>418.14499999999998</v>
+      </c>
+      <c r="AQ29">
+        <v>399</v>
       </c>
       <c r="AR29">
-        <v>0</v>
+        <v>355</v>
       </c>
       <c r="AS29">
         <v>0</v>
@@ -8711,7 +8714,7 @@
         <v>359</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="AO30">
         <v>164</v>
@@ -8720,10 +8723,10 @@
         <v>165</v>
       </c>
       <c r="AQ30">
-        <v>166</v>
+        <v>418.166</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>356</v>
       </c>
       <c r="AS30">
         <v>0</v>
@@ -8977,7 +8980,7 @@
         <v>419.80900000000003</v>
       </c>
       <c r="AN31">
-        <v>183</v>
+        <v>359.18299999999999</v>
       </c>
       <c r="AO31">
         <v>184</v>
@@ -8989,7 +8992,7 @@
         <v>186</v>
       </c>
       <c r="AR31">
-        <v>187</v>
+        <v>356.18700000000001</v>
       </c>
       <c r="AS31">
         <v>188</v>

--- a/map.xlsx
+++ b/map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/phamxuanbac/Downloads/gamedev/Game03/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94737AD5-A48F-E64C-99DB-2F5910F6FA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2C9EFA-C593-BE41-94D4-A642920968F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8177,7 +8177,7 @@
       <c r="CG25" s="1"/>
       <c r="CH25" s="1"/>
       <c r="CI25" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ25" s="1"/>
       <c r="CK25" s="1"/>
@@ -8435,7 +8435,7 @@
       <c r="CG26" s="1"/>
       <c r="CH26" s="1"/>
       <c r="CI26" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CJ26" s="1"/>
       <c r="CK26" s="1"/>
@@ -8705,7 +8705,7 @@
       <c r="CG27" s="1"/>
       <c r="CH27" s="1"/>
       <c r="CI27" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CJ27" s="1"/>
       <c r="CK27" s="1"/>
@@ -8975,7 +8975,7 @@
       <c r="CG28" s="1"/>
       <c r="CH28" s="1"/>
       <c r="CI28" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CJ28" s="1" t="s">
         <v>6</v>
